--- a/xls_files/Publications.xlsx
+++ b/xls_files/Publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e0a8ef36ec375223/Documents/pour portable/CARA website/xls_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{DCE4DBCF-FFC0-4A94-85B2-AC4C4A0D93C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A00FFAF1-8AF9-4C50-8DF8-62BF52855B1C}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="13_ncr:1_{DCE4DBCF-FFC0-4A94-85B2-AC4C4A0D93C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F7E097D-1D19-467F-B48B-85C7D96ADC24}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="871" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="390">
   <si>
     <t>Auteur1</t>
   </si>
@@ -949,9 +949,6 @@
     <t>M.Dion</t>
   </si>
   <si>
-    <t>Refined Trip Consolidation Framework and Extended Difference-in-Differences Analysis</t>
-  </si>
-  <si>
     <t>Projet</t>
   </si>
   <si>
@@ -1006,14 +1003,200 @@
     <t>https://www.sciencedirect.com/science/article/pii/S0167947325001859</t>
   </si>
   <si>
-    <t>North Actuarial Journal</t>
+    <t>1-38</t>
+  </si>
+  <si>
+    <t>Estimating the Causal Effect of Auto Insurance Claims on Driving Behaviour: A Heterogeneous Difference-in-Differences Approach with Imputation of Missing-Not-at-Random Outcomes</t>
+  </si>
+  <si>
+    <t>10.1111/jori.12172</t>
+  </si>
+  <si>
+    <t>10.3390/risks5040054</t>
+  </si>
+  <si>
+    <t>10.3390/risks4020012</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>10.1159/000450891</t>
+  </si>
+  <si>
+    <t>10.1214/16-AOAS914</t>
+  </si>
+  <si>
+    <t>10.1016/j.insmatheco.2016.01.003</t>
+  </si>
+  <si>
+    <t>10.1017/asb.2016.7</t>
+  </si>
+  <si>
+    <t>10.1080/10920277.2016.1161525</t>
+  </si>
+  <si>
+    <t>10.1016/j.insmatheco.2015.04.008</t>
+  </si>
+  <si>
+    <t>10.1017/asb.2015.6</t>
+  </si>
+  <si>
+    <t>10.1007/s13385-014-0097-9</t>
+  </si>
+  <si>
+    <t>10.1016/j.insmatheco.2014.06.012</t>
+  </si>
+  <si>
+    <t>10.1017/asb.2014.11</t>
+  </si>
+  <si>
+    <t>10.1007/s10666-013-9388-9</t>
+  </si>
+  <si>
+    <t>10.1017/asb.2013.20</t>
+  </si>
+  <si>
+    <t>10.1016/j.funbio.2012.12.003</t>
+  </si>
+  <si>
+    <t>10.66573/001c.90745</t>
+  </si>
+  <si>
+    <t>10.1080/03610920903447857</t>
+  </si>
+  <si>
+    <t>10.1080/03461231003690754</t>
+  </si>
+  <si>
+    <t>10.66573/001c.84248</t>
+  </si>
+  <si>
+    <t>10.1016/j.aap.2010.06.015</t>
+  </si>
+  <si>
+    <t>10.1111/j.1539-6975.2009.01321.x</t>
+  </si>
+  <si>
+    <t>10.1007/BF03191908</t>
+  </si>
+  <si>
+    <t>10.32614/RJ-2009-005</t>
+  </si>
+  <si>
+    <t>10.18637/jss.v025.i07</t>
+  </si>
+  <si>
+    <t>10.66573/001c.142045</t>
+  </si>
+  <si>
+    <t>10.1016/j.insmatheco.2007.08.003</t>
+  </si>
+  <si>
+    <t>10.1080/10920277.2007.10597487</t>
+  </si>
+  <si>
+    <t>10.1007/s11857-007-0003-5</t>
+  </si>
+  <si>
+    <t>10.2143/AST.36.1.2014153</t>
+  </si>
+  <si>
+    <t>10.3390/risks11110187</t>
+  </si>
+  <si>
+    <t>10.1007/s13385-026-00452-z</t>
+  </si>
+  <si>
+    <t>10.1017/asb.2026.10083</t>
+  </si>
+  <si>
+    <t>10.1016/j.csda.2025.108309</t>
+  </si>
+  <si>
+    <t>10.1016/j.insmatheco.2024.12.008</t>
+  </si>
+  <si>
+    <t>10.1017/S1748499524000113</t>
+  </si>
+  <si>
+    <t>10.1017/asb.2024.4</t>
+  </si>
+  <si>
+    <t>10.1017/S174849952300009X</t>
+  </si>
+  <si>
+    <t>10.1007/s13385-023-00355-3</t>
+  </si>
+  <si>
+    <t>10.1111/jori.12418</t>
+  </si>
+  <si>
+    <t>10.3390/risks10080152</t>
+  </si>
+  <si>
+    <t>10.1017/S1748499522000100</t>
+  </si>
+  <si>
+    <t>10.1080/10920277.2021.2022499</t>
+  </si>
+  <si>
+    <t>10.3390/risks9040058</t>
+  </si>
+  <si>
+    <t>10.1016/j.insmatheco.2021.01.008</t>
+  </si>
+  <si>
+    <t>10.66573/001c.29828</t>
+  </si>
+  <si>
+    <t>10.3390/risks8030091</t>
+  </si>
+  <si>
+    <t>10.1080/10920277.2020.1776623</t>
+  </si>
+  <si>
+    <t>10.1080/10920277.2019.1667830</t>
+  </si>
+  <si>
+    <t>10.3390/risks7030079</t>
+  </si>
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>10.7202/1106754ar</t>
+  </si>
+  <si>
+    <t>10.1007/978-0-8176-4626-4_4</t>
+  </si>
+  <si>
+    <t>10.1017/asb.2021.22</t>
+  </si>
+  <si>
+    <t>10.1080/10920277.2023.2218897</t>
+  </si>
+  <si>
+    <t>10.66573/001c.115924</t>
+  </si>
+  <si>
+    <t>10.1080/10920277.2023.2202707</t>
+  </si>
+  <si>
+    <t>10.66573/001c.130025</t>
+  </si>
+  <si>
+    <t>10.1080/10920277.2025.2456591</t>
+  </si>
+  <si>
+    <t>10.7202/1091875ar</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1155,6 +1338,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1499,11 +1687,14 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1561,6 +1752,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1860,15 +2055,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N82"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:O82"/>
+  <sheetFormatPr defaultRowHeight="14.6"/>
   <cols>
-    <col min="8" max="8" width="81.73046875" customWidth="1"/>
-    <col min="9" max="9" width="29.1328125" customWidth="1"/>
-    <col min="10" max="10" width="29.73046875" customWidth="1"/>
+    <col min="8" max="8" width="81.69140625" customWidth="1"/>
+    <col min="9" max="9" width="29.15234375" customWidth="1"/>
+    <col min="10" max="10" width="29.69140625" customWidth="1"/>
+    <col min="11" max="11" width="21.23046875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="29.69140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1911,8 +2108,11 @@
       <c r="N1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1935,16 +2135,19 @@
         <v>2026</v>
       </c>
       <c r="H2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.45">
+        <v>315</v>
+      </c>
+      <c r="O2" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1967,16 +2170,19 @@
         <v>2026</v>
       </c>
       <c r="H3" t="s">
+        <v>316</v>
+      </c>
+      <c r="L3" t="s">
+        <v>309</v>
+      </c>
+      <c r="M3" t="s">
         <v>317</v>
       </c>
-      <c r="L3" t="s">
-        <v>310</v>
-      </c>
-      <c r="M3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1984,7 +2190,7 @@
         <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D4" t="s">
         <v>16</v>
@@ -1999,16 +2205,19 @@
         <v>2026</v>
       </c>
       <c r="H4" t="s">
+        <v>313</v>
+      </c>
+      <c r="L4" t="s">
+        <v>309</v>
+      </c>
+      <c r="M4" t="s">
         <v>314</v>
       </c>
-      <c r="L4" t="s">
-        <v>310</v>
-      </c>
-      <c r="M4" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O4" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
         <v>152</v>
       </c>
@@ -2031,16 +2240,19 @@
         <v>2026</v>
       </c>
       <c r="H5" t="s">
+        <v>328</v>
+      </c>
+      <c r="L5" t="s">
         <v>309</v>
       </c>
-      <c r="L5" t="s">
-        <v>310</v>
-      </c>
       <c r="M5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
+        <v>311</v>
+      </c>
+      <c r="O5" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -2063,7 +2275,7 @@
         <v>2026</v>
       </c>
       <c r="H6" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="L6" t="s">
         <v>301</v>
@@ -2071,8 +2283,11 @@
       <c r="M6" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -2101,10 +2316,13 @@
         <v>301</v>
       </c>
       <c r="M7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
+        <v>310</v>
+      </c>
+      <c r="O7" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -2130,22 +2348,19 @@
         <v>290</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="J8" t="s">
-        <v>328</v>
-      </c>
-      <c r="K8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
+        <v>301</v>
       </c>
       <c r="M8" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O8" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
         <v>24</v>
       </c>
@@ -2168,14 +2383,14 @@
         <v>2026</v>
       </c>
       <c r="H9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" t="s">
         <v>48</v>
       </c>
       <c r="K9" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="L9" t="s">
         <v>39</v>
@@ -2183,8 +2398,11 @@
       <c r="M9" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O9" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -2215,8 +2433,8 @@
       <c r="J10" t="s">
         <v>48</v>
       </c>
-      <c r="K10" t="s">
-        <v>320</v>
+      <c r="K10" s="3" t="s">
+        <v>327</v>
       </c>
       <c r="L10" t="s">
         <v>39</v>
@@ -2224,8 +2442,11 @@
       <c r="M10" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O10" s="3" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
         <v>17</v>
       </c>
@@ -2251,7 +2472,7 @@
         <v>291</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="J11" t="s">
         <v>34</v>
@@ -2265,8 +2486,11 @@
       <c r="M11" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O11" s="3" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" t="s">
         <v>27</v>
       </c>
@@ -2289,10 +2513,10 @@
         <v>2025</v>
       </c>
       <c r="H12" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="J12" t="s">
         <v>304</v>
@@ -2306,8 +2530,11 @@
       <c r="M12" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O12" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -2344,8 +2571,11 @@
       <c r="M13" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O13" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
         <v>27</v>
       </c>
@@ -2385,8 +2615,11 @@
       <c r="M14" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O14" s="3" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
         <v>21</v>
       </c>
@@ -2426,8 +2659,11 @@
       <c r="M15" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O15" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -2467,8 +2703,11 @@
       <c r="M16" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O16" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2508,8 +2747,11 @@
       <c r="M17" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O17" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="A18" t="s">
         <v>31</v>
       </c>
@@ -2549,8 +2791,11 @@
       <c r="M18" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O18" s="1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -2573,7 +2818,7 @@
         <v>2023</v>
       </c>
       <c r="H19" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I19" t="s">
         <v>36</v>
@@ -2590,8 +2835,11 @@
       <c r="M19" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O19" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -2631,8 +2879,11 @@
       <c r="M20" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O20" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
       <c r="A21" t="s">
         <v>27</v>
       </c>
@@ -2672,8 +2923,11 @@
       <c r="M21" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O21" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" t="s">
         <v>14</v>
       </c>
@@ -2713,8 +2967,11 @@
       <c r="M22" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O22" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -2754,8 +3011,11 @@
       <c r="M23" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O23" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -2795,8 +3055,11 @@
       <c r="M24" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O24" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -2836,8 +3099,11 @@
       <c r="M25" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O25" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" t="s">
         <v>31</v>
       </c>
@@ -2877,8 +3143,11 @@
       <c r="M26" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O26" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2918,8 +3187,11 @@
       <c r="M27" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O27" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2956,8 +3228,11 @@
       <c r="M28" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O28" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="A29" t="s">
         <v>83</v>
       </c>
@@ -2997,8 +3272,11 @@
       <c r="M29" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O29" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -3038,8 +3316,11 @@
       <c r="M30" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O30" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="A31" t="s">
         <v>14</v>
       </c>
@@ -3079,8 +3360,11 @@
       <c r="M31" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O31" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="A32" t="s">
         <v>17</v>
       </c>
@@ -3120,8 +3404,11 @@
       <c r="M32" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O32" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -3161,8 +3448,11 @@
       <c r="M33" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O33" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="A34" t="s">
         <v>24</v>
       </c>
@@ -3202,8 +3492,11 @@
       <c r="M34" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O34" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
       <c r="A35" t="s">
         <v>110</v>
       </c>
@@ -3243,8 +3536,11 @@
       <c r="M35" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O35" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -3284,8 +3580,11 @@
       <c r="M36" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O36" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -3322,8 +3621,11 @@
       <c r="M37" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O37" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15">
       <c r="A38" t="s">
         <v>126</v>
       </c>
@@ -3357,8 +3659,11 @@
       <c r="L38" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O38" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -3392,8 +3697,11 @@
       <c r="L39" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O39" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15">
       <c r="A40" t="s">
         <v>135</v>
       </c>
@@ -3427,8 +3735,11 @@
       <c r="L40" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O40" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -3459,8 +3770,11 @@
       <c r="L41" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O41" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15">
       <c r="A42" t="s">
         <v>141</v>
       </c>
@@ -3494,8 +3808,11 @@
       <c r="L42" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O42" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15">
       <c r="A43" t="s">
         <v>126</v>
       </c>
@@ -3529,8 +3846,11 @@
       <c r="L43" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O43" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="A44" t="s">
         <v>152</v>
       </c>
@@ -3564,8 +3884,11 @@
       <c r="L44" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O44" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -3599,8 +3922,11 @@
       <c r="L45" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O45" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
       <c r="A46" t="s">
         <v>152</v>
       </c>
@@ -3634,8 +3960,11 @@
       <c r="L46" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O46" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -3669,8 +3998,11 @@
       <c r="L47" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="O47" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15">
       <c r="A48" t="s">
         <v>152</v>
       </c>
@@ -3704,8 +4036,11 @@
       <c r="L48" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O48" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49" t="s">
         <v>15</v>
       </c>
@@ -3739,8 +4074,11 @@
       <c r="L49" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O49" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50" t="s">
         <v>15</v>
       </c>
@@ -3774,8 +4112,11 @@
       <c r="L50" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O50" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -3809,8 +4150,11 @@
       <c r="L51" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O51" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52" t="s">
         <v>179</v>
       </c>
@@ -3844,8 +4188,11 @@
       <c r="L52" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O52" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53" t="s">
         <v>15</v>
       </c>
@@ -3879,8 +4226,11 @@
       <c r="L53" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O53" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54" t="s">
         <v>186</v>
       </c>
@@ -3914,8 +4264,11 @@
       <c r="L54" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O54" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -3949,8 +4302,11 @@
       <c r="L55" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O55" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -3984,8 +4340,11 @@
       <c r="L56" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O56" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -4016,8 +4375,11 @@
       <c r="L57" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O57" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -4048,8 +4410,11 @@
       <c r="L58" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O58" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -4083,8 +4448,11 @@
       <c r="L59" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O59" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -4115,8 +4483,11 @@
       <c r="L60" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O60" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -4150,8 +4521,11 @@
       <c r="L61" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O61" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -4185,8 +4559,11 @@
       <c r="L62" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O62" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63" t="s">
         <v>15</v>
       </c>
@@ -4220,8 +4597,11 @@
       <c r="L63" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O63" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -4255,8 +4635,11 @@
       <c r="L64" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O64" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -4290,8 +4673,11 @@
       <c r="L65" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O65" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -4325,8 +4711,11 @@
       <c r="L66" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O66" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
       <c r="A67" t="s">
         <v>194</v>
       </c>
@@ -4360,8 +4749,11 @@
       <c r="L67" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O67" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -4392,8 +4784,11 @@
       <c r="L68" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O68" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -4427,8 +4822,11 @@
       <c r="L69" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O69" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -4462,8 +4860,11 @@
       <c r="L70" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O70" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -4497,8 +4898,11 @@
       <c r="L71" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O71" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15">
       <c r="A72" t="s">
         <v>240</v>
       </c>
@@ -4532,8 +4936,11 @@
       <c r="L72" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O72" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
       <c r="A73" t="s">
         <v>240</v>
       </c>
@@ -4567,8 +4974,11 @@
       <c r="L73" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O73" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
       <c r="A74" t="s">
         <v>248</v>
       </c>
@@ -4602,8 +5012,11 @@
       <c r="L74" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O74" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -4637,8 +5050,11 @@
       <c r="L75" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O75" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -4672,8 +5088,11 @@
       <c r="L76" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O76" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -4707,8 +5126,11 @@
       <c r="L77" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O77" s="4" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -4742,8 +5164,11 @@
       <c r="L78" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O78" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -4777,8 +5202,11 @@
       <c r="L79" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="O79" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -4812,8 +5240,11 @@
       <c r="L80" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O80" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="81" spans="1:15">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -4847,8 +5278,11 @@
       <c r="L81" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.45">
+      <c r="O81" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15">
       <c r="A82" t="s">
         <v>152</v>
       </c>
@@ -4890,6 +5324,9 @@
       </c>
       <c r="N82">
         <v>1</v>
+      </c>
+      <c r="O82" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
